--- a/manuscript/robustness/Supplemental_Table_1.xlsx
+++ b/manuscript/robustness/Supplemental_Table_1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Excitatory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inhibitory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Astrocytes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="All cell types" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Microglia" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="References" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Cell Types" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excitatory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inhibitory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astrocytes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Microglia" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Excitatory'!$A$1:$K$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inhibitory'!$A$1:$K$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Astrocytes'!$A$1:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All cell types'!$A$1:$K$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Cell Types'!$A$1:$K$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Excitatory'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inhibitory'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Astrocytes'!$A$1:$K$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Microglia'!$A$1:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'References'!$A$1:$C$54</definedName>
   </definedNames>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>p-value (DE)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -589,54 +589,54 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HSP90AA1</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>WWOX</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.7343377</v>
+        <v>0.08729035</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1.762354243774555e-209</v>
+        <v>7.701748886382555e-07</v>
       </c>
       <c r="F2" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0.0384615384615384</v>
       </c>
       <c r="I2" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Dickey 2007; Luo 2007</t>
+          <t>Kunkle 2019; Sze 2004</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Chaperone that stabilizes phospho-tau</t>
+          <t>WW domain-containing oxidoreductase. AD risk locus (Kunkle 2019); reduced WWOX expression increases tau phosphorylation in vitro (Sze 2004).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MAP1B</t>
+          <t>NCAM2</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.22427803</v>
+        <v>0.22656935</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4.329589917707005e-104</v>
+        <v>3.363724983693674e-71</v>
       </c>
       <c r="F3" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -664,22 +664,22 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>Hasegawa 1990</t>
+          <t>Leshchyns'ka 2015; Sytnyk 2017</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Phosphorylated MAP1B fragments are bound to neurofibrillary tangles</t>
+          <t>Neural cell adhesion molecule 2. Amyloid-beta binds NCAM2 and depletes it from synapses, contributing to synapse loss; NCAM2 is reduced in AD hippocampus (Leshchyns'ka 2015; Sytnyk 2017).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AKAP9</t>
+          <t>HSP90AA1</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -688,41 +688,41 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.12968345</v>
+        <v>0.6729497</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.543043063061846e-07</v>
+        <v>1.611631363929448e-230</v>
       </c>
       <c r="F4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I4" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>Logue 2014; Ikezu 2018</t>
+          <t>Dickey 2007; Luo 2007</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Rare variants associated with AD in African Americans (Logue 2014); variants raise tau phosphorylation in patient cell lines (Ikezu 2018)</t>
+          <t>Molecular chaperone. Stabilizes phosphorylated tau; HSP90 inhibition promotes tau degradation through CHIP and reduces tau pathology in models (Dickey 2007; Luo 2007).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LRP1B</t>
+          <t>ERBB4</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.0077264565</v>
+        <v>-0.05952082</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.292516248941438e-05</v>
+        <v>0.0037938456457026</v>
       </c>
       <c r="F5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -750,22 +750,22 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Cam 2004</t>
+          <t>Chaudhury 2003; Woo 2011</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Binds APP, keeps it at the cell surface, and reduces amyloid-beta production (cell models)</t>
+          <t>Neuregulin receptor tyrosine kinase. Increased in AD neurons and APP/PS1 mice (Woo 2011); neuregulin-1 and ERBB4 immunoreactivity associated with neuritic plaques (Chaudhury 2003).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DPP10</t>
+          <t>CNTN5</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.023014318</v>
+        <v>0.09835521</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.000630871792779</v>
+        <v>7.047255488836244e-12</v>
       </c>
       <c r="F6" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -793,22 +793,22 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Chen 2014</t>
+          <t>Dauar 2023; Whitehouse 2013</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Present in AD tangles; partner of the Kv4 potassium channel (pathway-level)</t>
+          <t>Neuronal adhesion molecule of the contactin family. A risk variant is associated with AD pathology and progression measures (Dauar 2023); CNTN5 protein was unchanged in a separate AD brain series (Whitehouse 2013).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CNTNAP2</t>
+          <t>DPP10</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.050843682</v>
+        <v>-0.04691517</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.276144168833856e-24</v>
+        <v>0.3933888731634747</v>
       </c>
       <c r="F7" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -836,126 +836,126 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>van Abel 2012; Jansen 2019</t>
+          <t>Chen 2014</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Rare-variant AD risk locus in Jansen 2019 (one cohort, not tested in Wightman 2021); reduced in late-onset AD hippocampus via STOX1A repression</t>
+          <t>Dipeptidyl peptidase-like subunit of Kv4 potassium channels. Abnormally expressed and present in neurofibrillary tangles in AD and other neurodegenerative diseases (Chen 2014).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SNHG14</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
+          <t>HS6ST3</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.15186132</v>
+        <v>-0.0344914</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4.096430819233685e-107</v>
+        <v>0.9965523604844416</v>
       </c>
       <c r="F8" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Cai 2021; Xie 2024; Runte 2001</t>
+          <t>Rauch 2018; Stopschinski 2018</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Emerging: expression-only evidence (raised in AD serum in one study; one AD brain cell subcluster in a reanalysis); no genetic or functional AD data. Imprinted lncRNA (long noncoding RNA)</t>
+          <t>Heparan sulfate 6-O-sulfotransferase. Heparan sulfate 6-O-sulfation controls neuronal uptake of tau (Rauch 2018; Stopschinski 2018); those studies examined other family members.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>LUC7L3</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>PDE4B</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.12897867</v>
+        <v>-0.029262813</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4.240577641583623e-19</v>
+        <v>0.0001304924615354</v>
       </c>
       <c r="F9" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Armstrong 2024</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>cAMP phosphodiesterase 4B. A hypomorphic Pde4b allele prevents memory and brain metabolism deficits in an App knock-in AD mouse (Armstrong 2024); genetic association with AD cited in that study.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LRFN5</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>SNHG14</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1948824</v>
+        <v>0.036285296</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5.044556840582442e-110</v>
+        <v>2.169560720898356e-38</v>
       </c>
       <c r="F10" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -963,38 +963,42 @@
       <c r="I10" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Cai 2021; Xie 2024; Runte 2001</t>
+        </is>
+      </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Imprinted lncRNA host of snoRNAs and the UBE3A antisense transcript (Runte 2001). Increased in AD serum in one study (Cai 2021) and marks an AD brain cell subcluster in a reanalysis (Xie 2024); no genetic or functional AD data.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COPG2</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>DOCK4</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.019945797</v>
+        <v>0.07413366</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.009158713320448901</v>
+        <v>4.553924977266265e-05</v>
       </c>
       <c r="F11" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1004,161 +1008,169 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Bone 2021; Bellenguez 2022</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Rac guanine nucleotide exchange factor. Low-frequency coding variant found only in a joint AD and cardiometabolic trait analysis (Bone 2021); not a locus in Bellenguez 2022; no functional AD data.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TENM2</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>SPOCK1</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.103909455</v>
+        <v>0.09085624</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2.400386731864214e-42</v>
+        <v>1.005503898987354e-07</v>
       </c>
       <c r="F12" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I12" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="8" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Ekenel 2025; Bellenguez 2022</t>
+        </is>
+      </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Proteoglycan testican-1. GWAS signal reported by one group and not a locus in Bellenguez 2022; follow-up limited to a conference abstract in cell lines (Ekenel 2025).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RBM25</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RALYL</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.16780527</v>
+        <v>0.11111467</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>6.664736604865236e-11</v>
+        <v>3.437049732044309e-50</v>
       </c>
       <c r="F13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0.0384615384615384</v>
       </c>
       <c r="I13" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Zhang 2020</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Neuronal RNA-binding protein. Expression falls with AD severity and is higher in individuals with cognitive reserve (Zhang 2020); expression data only.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SRSF11</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>LUC7L3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.053360738</v>
+        <v>0.19691005</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0001186740407618</v>
+        <v>6.92225694461615e-44</v>
       </c>
       <c r="F14" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I14" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PNISR</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RBM25</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.11220688</v>
+        <v>0.16779387</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2.722208993379257e-12</v>
+        <v>1.969044936991839e-09</v>
       </c>
       <c r="F15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1166,38 +1178,42 @@
       <c r="I15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="8" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CDH12</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>QKI</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.18920773</v>
+        <v>0.19170265</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3.16271206215448e-78</v>
+        <v>0.0001341224521875</v>
       </c>
       <c r="F16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1205,38 +1221,42 @@
       <c r="I16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Farnsworth 2016</t>
+        </is>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Glial RNA-binding protein. Increased in AD brain, with expression tracking APP, PSEN1, PSEN2 and MAPT (Farnsworth 2016); expression data only.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ANKRD26</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>ZEB2</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.18217914</v>
+        <v>-0.12610558</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.616234615633171e-17</v>
+        <v>1.403294970199935e-13</v>
       </c>
       <c r="F17" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1244,63 +1264,67 @@
       <c r="I17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="8" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Yanaizu 2025</t>
+        </is>
+      </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Zinc finger E-box-binding transcription factor. Promotes TREM2 expression in a human microglial cell line (Yanaizu 2025); no AD tissue or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ANKRD12</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>PLXDC2</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4649069</v>
+        <v>0.29034597</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.4550959251418e-64</v>
+        <v>2.92444674091081e-26</v>
       </c>
       <c r="F18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0.0384615384615384</v>
       </c>
       <c r="I18" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Oh 2025</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Plexin domain-containing transmembrane receptor enriched in microglia. Increased in AD brain and cerebrospinal fluid; overexpression impairs amyloid-beta uptake in a microglial cell line (Oh 2025); no in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PRRC2C</t>
+          <t>KCNIP4</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1309,37 +1333,41 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.13426594</v>
+        <v>0.015608293</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1.659005203161331e-07</v>
+        <v>3.830344240127848e-11</v>
       </c>
       <c r="F19" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I19" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J19" s="8" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Morohashi 2002; Bellenguez 2022</t>
+        </is>
+      </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Calsenilin-like EF-hand protein (CALP/KChIP4). Binds presenilin 2 and Kv4 channels without altering amyloid processing (Morohashi 2002); not a risk locus in Bellenguez 2022.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ENSG00000274422</t>
+          <t>COPG2</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1348,16 +1376,16 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.32478172</v>
+        <v>-0.051300593</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4.117946476901092e-10</v>
+        <v>0.0523978305406472</v>
       </c>
       <c r="F20" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1365,20 +1393,24 @@
       <c r="I20" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="8" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>COPI coat subunit for Golgi vesicle transport. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BDP1</t>
+          <t>SLC24A2</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1387,37 +1419,41 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2600565</v>
+        <v>0.032657485</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7.275264506958522e-33</v>
+        <v>2.3823185962033e-07</v>
       </c>
       <c r="F21" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I21" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="8" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Potassium-dependent sodium/calcium exchanger (NCKX2). No AD-specific studies; the AD risk locus is the related gene SLC24A4.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TAFA2</t>
+          <t>ANKRD12</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -1426,37 +1462,41 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.17256476</v>
+        <v>0.4575935</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.911280905483247e-43</v>
+        <v>2.216411671586616e-74</v>
       </c>
       <c r="F22" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Ankyrin repeat transcriptional corepressor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>EPIC1</t>
+          <t>FRMD5</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -1465,75 +1505,853 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.03606564</v>
+        <v>0.07288448</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.5789377427576567</v>
+        <v>2.571019965738418e-10</v>
       </c>
       <c r="F23" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.1153846153846153</v>
       </c>
       <c r="I23" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J23" s="8" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>FERM domain protein. No AD-specific studies; the AD-associated family members are FRMD4A and FRMD6.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>FHIT</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.12219529</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.958546800258247e-12</v>
+      </c>
+      <c r="F24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Fragile histidine triad tumor suppressor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ROBO2</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-0.14253674</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1.174744392914619e-07</v>
+      </c>
+      <c r="F25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>SLIT receptor for axon guidance. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>PLCL1</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.13310342</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.0050309767432661</v>
+      </c>
+      <c r="F26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Catalytically inactive phospholipase C-like protein that regulates GABA-A receptor trafficking. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ELMO1</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.020089554</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.0004319706725633</v>
+      </c>
+      <c r="F27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Rac activator in cell engulfment and phagocytosis. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>NPAS3</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.20711255</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.597992110933664e-24</v>
+      </c>
+      <c r="F28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Neuronal PAS domain transcription factor linked to psychiatric disorders. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SLC44A1</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.15670578</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.0154747679463562</v>
+      </c>
+      <c r="F29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Fagerberg 2020; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Choline transporter-like protein 1. Loss-of-function variants cause a childhood-onset neurodegenerative disease (Fagerberg 2020); not associated with AD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ARAP2</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.27938163</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.007482785636981e-24</v>
+      </c>
+      <c r="F30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Arf and Rho GTPase-activating protein. Suggestive signal in a GWAS of AD endophenotypes only; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>MAN2A1</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-0.20885615</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>3.201874853020317e-33</v>
+      </c>
+      <c r="F31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Dube 2019; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Golgi alpha-mannosidase II. A circular RNA from this locus (circMAN2A1) is altered in AD brain (Dube 2019); no AD studies of the MAN2A1 protein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>DPYD</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.2428678</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>7.083351251966565e-18</v>
+      </c>
+      <c r="F32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Dihydropyrimidine dehydrogenase in pyrimidine catabolism. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>GRID2</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.053968597</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.0033080792048531</v>
+      </c>
+      <c r="F33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Delta-2 glutamate receptor that organizes cerebellar synapses. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>DIP2B</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.00021104331</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.0002680158544316</v>
+      </c>
+      <c r="F34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Regulates axon outgrowth through tubulin acetylation. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>FRYL</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0.06093571</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.4398057750248119</v>
+      </c>
+      <c r="F35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Furry-like protein involved in cell morphology. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>TCF12</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.040693924</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.5478841195561135</v>
+      </c>
+      <c r="F36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>E-protein basic helix-loop-helix transcription factor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>ZC3H13</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0.1027448</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.0465321622222441</v>
-      </c>
-      <c r="F24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="D37" s="4" t="n">
+        <v>0.12422563</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.0306440062356844</v>
+      </c>
+      <c r="F37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Knuckles 2018; Huang 2020</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>Part of the m6A (N6-methyladenosine) methylation complex; AD evidence is for METTL3, not ZC3H13</t>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Component of the m6A (N6-methyladenosine) writer complex (Knuckles 2018). AD studies report altered METTL3 in the same complex (Huang 2020), not ZC3H13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>EDIL3</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.31071475</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>1.085984614386102e-32</v>
+      </c>
+      <c r="F38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I38" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Secreted integrin ligand of the extracellular matrix. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ZNF91</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-0.108737394</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1.568412335075166e-12</v>
+      </c>
+      <c r="F39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>KRAB zinc finger protein that represses SVA retrotransposons. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ENSG00000230021</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.6634869</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>5.454691897364666e-113</v>
+      </c>
+      <c r="F40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I40" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Unannotated transcript without an assigned gene symbol; no AD literature linked to this identifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>PIP4K2A</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0.2727138</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>7.34739456580919e-07</v>
+      </c>
+      <c r="F41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Nguyen 2024; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Phosphatidylinositol-5-phosphate 4-kinase. Identified only in a bioinformatic blood transcriptome analysis of AD with type 2 diabetes (Nguyen 2024); no tissue or functional AD data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SLAIN1</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.13132645</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.3643079313496823</v>
+      </c>
+      <c r="F42" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Microtubule plus-end tracking protein. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:K42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1583,7 +2401,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>p-value (DE)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1623,7 +2441,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TMSB4X</t>
+          <t>HSP90AA1</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1632,41 +2450,41 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-1.0677145</v>
+        <v>0.7343377</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>8.460546846119662e-81</v>
+        <v>1.762354243774555e-209</v>
       </c>
       <c r="F2" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I2" s="6" t="b">
         <v>1</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Stem Cell Reports 2025</t>
+          <t>Dickey 2007; Luo 2007</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Reduced in AD excitatory neurons; thymosin beta 4 rescues amyloid and neuronal deficits in organoids and 5xFAD mice</t>
+          <t>Molecular chaperone. Stabilizes phosphorylated tau; HSP90 inhibition promotes tau degradation through CHIP and reduces tau pathology in models (Dickey 2007; Luo 2007).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HSP90AA1</t>
+          <t>MAP1B</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1675,16 +2493,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.5721981</v>
+        <v>0.22427803</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2.801923435222558e-103</v>
+        <v>4.329589917707005e-104</v>
       </c>
       <c r="F3" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1694,22 +2512,22 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>Dickey 2007; Luo 2007</t>
+          <t>Hasegawa 1990</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Chaperone that stabilizes phospho-tau</t>
+          <t>Microtubule-associated protein 1B. Phosphorylated MAP1B fragments are bound to neurofibrillary tangles (Hasegawa 1990).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ERBB4</t>
+          <t>AKAP9</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1718,41 +2536,41 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.17013964</v>
+        <v>0.12968345</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7.487643493129158e-92</v>
+        <v>1.543043063061846e-07</v>
       </c>
       <c r="F4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.1153846153846153</v>
       </c>
       <c r="I4" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>Chaudhury 2003; Woo 2011</t>
+          <t>Logue 2014; Ikezu 2018</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Increased in AD neurons and at plaques</t>
+          <t>A-kinase anchoring protein. Two rare missense variants associated with AD in African Americans (Logue 2014); patient cell lines carrying these variants show increased tau phosphorylation (Ikezu 2018).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SPARCL1</t>
+          <t>LRP1B</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1761,37 +2579,37 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.25811455</v>
+        <v>-0.0077264565</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.863357780448858e-30</v>
+        <v>2.292516248941438e-05</v>
       </c>
       <c r="F5" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Seddighi 2018; Cabral-Miranda 2025</t>
+          <t>Cam 2004</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Astrocyte-secreted synaptogenic protein (hevin); variants lowering expression linked to faster symptom onset (Seddighi 2018), but astrocytic overexpression is protective in AD mice (Cabral-Miranda 2025); direction unresolved</t>
+          <t>LDL receptor-related protein 1B. Binds APP, retains it at the cell surface, and lowers amyloid-beta production in cell models (Cam 2004).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -1804,19 +2622,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.27049708</v>
+        <v>-0.023014318</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4.747134946406992e-43</v>
+        <v>0.000630871792779</v>
       </c>
       <c r="F6" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I6" s="6" t="b">
         <v>0</v>
@@ -1828,7 +2646,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Present in AD tangles; partner of the Kv4 potassium channel (pathway-level)</t>
+          <t>Dipeptidyl peptidase-like subunit of Kv4 potassium channels. Abnormally expressed and present in neurofibrillary tangles in AD and other neurodegenerative diseases (Chen 2014).</t>
         </is>
       </c>
     </row>
@@ -1838,25 +2656,25 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ENO2</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
+          <t>CNTNAP2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.30213574</v>
+        <v>0.050843682</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.03822091495916e-09</v>
+        <v>1.276144168833856e-24</v>
       </c>
       <c r="F7" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1866,34 +2684,34 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>Schmidt 2014; Katayama 2021</t>
+          <t>van Abel 2012; Jansen 2019</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Emerging: CSF (cerebrospinal fluid) marker of neuronal injury, raised in AD by meta-analysis; no evidence it drives progression. Neuron-specific enolase</t>
+          <t>Contactin-associated neurexin-family protein. Rare-variant AD locus in one cohort of Jansen 2019; reduced in late-onset AD hippocampus through STOX1A repression (van Abel 2012).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SNTG1</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>SNHG14</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.28416392</v>
+        <v>0.15186132</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3.846748676542297e-157</v>
+        <v>4.096430819233685e-107</v>
       </c>
       <c r="F8" s="6" t="b">
         <v>0</v>
@@ -1905,40 +2723,44 @@
         <v>0.0769230769230769</v>
       </c>
       <c r="I8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Cai 2021; Xie 2024; Runte 2001</t>
+        </is>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Imprinted lncRNA host of snoRNAs and the UBE3A antisense transcript (Runte 2001). Increased in AD serum in one study (Cai 2021) and marks an AD brain cell subcluster in a reanalysis (Xie 2024); no genetic or functional AD data.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ROBO2</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>LUC7L3</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.061422046</v>
+        <v>0.12897867</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6.1220197234444e-17</v>
+        <v>4.240577641583623e-19</v>
       </c>
       <c r="F9" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1948,40 +2770,40 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Bishof 2018</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LUC7L3</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RBM25</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.35283738</v>
+        <v>0.16780527</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.707468400566502e-88</v>
+        <v>6.664736604865236e-11</v>
       </c>
       <c r="F10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -1991,61 +2813,65 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Bishof 2018</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KIAA1217</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>SRSF11</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.06522965999999999</v>
+        <v>0.053360738</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.328093317299795e-08</v>
+        <v>0.0001186740407618</v>
       </c>
       <c r="F11" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="8" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Wu 2006</t>
+        </is>
+      </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Serine/arginine-rich splicing factor (SRp54). Represses tau exon 10 inclusion and so shifts the 3R/4R tau balance in cell assays (Wu 2006); no AD-specific data.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RBM25</t>
+          <t>LRFN5</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -2054,16 +2880,16 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.50209945</v>
+        <v>0.1948824</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4.513745564190749e-68</v>
+        <v>5.044556840582442e-110</v>
       </c>
       <c r="F12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -2078,17 +2904,17 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Synaptic adhesion-like molecule (SALM5). No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ANKRD12</t>
+          <t>COPG2</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -2097,16 +2923,16 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4475533</v>
+        <v>0.019945797</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1.897923366348756e-57</v>
+        <v>0.009158713320448901</v>
       </c>
       <c r="F13" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -2121,17 +2947,17 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>COPI coat subunit for Golgi vesicle transport. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PRRC2C</t>
+          <t>TENM2</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -2140,37 +2966,41 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.32917583</v>
+        <v>0.103909455</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>9.785501376641174e-31</v>
+        <v>2.400386731864214e-42</v>
       </c>
       <c r="F14" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I14" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Med Hypotheses 2015; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Teneurin-2 synaptic adhesion protein. Discussed only in a hypothesis paper on the teneurin family (Med Hypotheses 2015); no AD data for TENM2.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SGCZ</t>
+          <t>PNISR</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -2179,10 +3009,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.119287975</v>
+        <v>0.11220688</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1.811905876464507e-15</v>
+        <v>2.722208993379257e-12</v>
       </c>
       <c r="F15" s="6" t="b">
         <v>0</v>
@@ -2196,10 +3026,14 @@
       <c r="I15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="8" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Nuclear serine/arginine-rich splicing-associated protein. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2209,7 +3043,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LINC00342</t>
+          <t>CDH12</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -2218,16 +3052,16 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.11878686</v>
+        <v>0.18920773</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.757621790043772e-09</v>
+        <v>3.16271206215448e-78</v>
       </c>
       <c r="F16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -2235,10 +3069,14 @@
       <c r="I16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Brain-expressed type II classical cadherin. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2248,7 +3086,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ENSG00000274422</t>
+          <t>ANKRD26</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2257,10 +3095,10 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9888332</v>
+        <v>0.18217914</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>9.326740078405216e-77</v>
+        <v>1.616234615633171e-17</v>
       </c>
       <c r="F17" s="6" t="b">
         <v>0</v>
@@ -2272,12 +3110,16 @@
         <v>0.0384615384615384</v>
       </c>
       <c r="I17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Ankyrin repeat protein; germline variants cause inherited thrombocytopenia. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2287,7 +3129,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DYNC2I1</t>
+          <t>ANKRD12</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2296,27 +3138,31 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.107587874</v>
+        <v>0.4649069</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.939190509593427e-07</v>
+        <v>1.4550959251418e-64</v>
       </c>
       <c r="F18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0.0384615384615384</v>
       </c>
       <c r="I18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Ankyrin repeat transcriptional corepressor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +3172,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MGAT4C</t>
+          <t>PRRC2C</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2335,27 +3181,31 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.09757373</v>
+        <v>0.13426594</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1.470835717150639e-08</v>
+        <v>1.659005203161331e-07</v>
       </c>
       <c r="F19" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I19" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J19" s="8" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Proline-rich coiled-coil protein and stress granule component. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2365,7 +3215,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PPIG</t>
+          <t>ENSG00000274422</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2374,27 +3224,31 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.24191454</v>
+        <v>0.32478172</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>9.143039382956179e-06</v>
+        <v>4.117946476901092e-10</v>
       </c>
       <c r="F20" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I20" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="8" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Unannotated transcript without an assigned gene symbol; no AD literature linked to this identifier.</t>
         </is>
       </c>
     </row>
@@ -2404,7 +3258,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ENSG00000230021</t>
+          <t>BDP1</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2413,22 +3267,22 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5416309</v>
+        <v>-0.2600565</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>3.717986044742603e-47</v>
+        <v>7.275264506958522e-33</v>
       </c>
       <c r="F21" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I21" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
@@ -2437,7 +3291,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Subunit of the RNA polymerase III initiation factor TFIIIB. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2447,7 +3301,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ZC3H13</t>
+          <t>TAFA2</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2456,16 +3310,16 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.19416435</v>
+        <v>0.17256476</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.0005186457807994</v>
+        <v>1.911280905483247e-43</v>
       </c>
       <c r="F22" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -2475,12 +3329,12 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Knuckles 2018; Huang 2020</t>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Part of the m6A (N6-methyladenosine) methylation complex; AD evidence is for METTL3, not ZC3H13</t>
+          <t>Brain-expressed secreted chemokine-like protein. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +3344,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GALNTL6</t>
+          <t>EPIC1</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2499,27 +3353,31 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.09235255000000001</v>
+        <v>-0.03606564</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.0389757839474736</v>
+        <v>0.5789377427576567</v>
       </c>
       <c r="F23" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I23" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J23" s="8" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Sun 2019</t>
+        </is>
+      </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>MYC-interacting lncRNA. Protects cultured neurons from oxidative injury (Sun 2019); not studied in AD.</t>
         </is>
       </c>
     </row>
@@ -2529,7 +3387,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SREK1</t>
+          <t>ZC3H13</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2538,16 +3396,16 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.61310506</v>
+        <v>0.1027448</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.473914604291229e-32</v>
+        <v>0.0465321622222441</v>
       </c>
       <c r="F24" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -2555,10 +3413,14 @@
       <c r="I24" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="8" t="n"/>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Knuckles 2018; Huang 2020</t>
+        </is>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Component of the m6A (N6-methyladenosine) writer complex (Knuckles 2018). AD studies report altered METTL3 in the same complex (Huang 2020), not ZC3H13.</t>
         </is>
       </c>
     </row>
@@ -2569,6 +3431,1080 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bin</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>logFC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p-value (DE)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>recurSieve_Unique</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Seed stability</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>recurSieve p-value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Found in baseline RF</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TMSB4X</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>-1.0677145</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>8.460546846119662e-81</v>
+      </c>
+      <c r="F2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.1153846153846153</v>
+      </c>
+      <c r="I2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Zeng 2025</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Thymosin beta 4. Reduced in neurons of familial AD organoids and in excitatory neurons of AD brain; thymosin beta 4 treatment reduces amyloid and neuronal deficits in organoids and AD model mice (Zeng 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>HSP90AA1</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.5721981</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2.801923435222558e-103</v>
+      </c>
+      <c r="F3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Dickey 2007; Luo 2007</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Molecular chaperone. Stabilizes phosphorylated tau; HSP90 inhibition promotes tau degradation through CHIP and reduces tau pathology in models (Dickey 2007; Luo 2007).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ERBB4</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.17013964</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.487643493129158e-92</v>
+      </c>
+      <c r="F4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Chaudhury 2003; Woo 2011</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Neuregulin receptor tyrosine kinase. Increased in AD neurons and APP/PS1 mice (Woo 2011); neuregulin-1 and ERBB4 immunoreactivity associated with neuritic plaques (Chaudhury 2003).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SPARCL1</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.25811455</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.863357780448858e-30</v>
+      </c>
+      <c r="F5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Seddighi 2018; Cabral-Miranda 2025</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Astrocyte-secreted synaptogenic protein (hevin). Variants lowering expression are linked to earlier symptom onset (Seddighi 2018), whereas astrocytic overexpression is protective in AD mice (Cabral-Miranda 2025); direction of effect unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DPP10</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.27049708</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.747134946406992e-43</v>
+      </c>
+      <c r="F6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Chen 2014</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Dipeptidyl peptidase-like subunit of Kv4 potassium channels. Abnormally expressed and present in neurofibrillary tangles in AD and other neurodegenerative diseases (Chen 2014).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ENO2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.30213574</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.03822091495916e-09</v>
+      </c>
+      <c r="F7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Schmidt 2014; Katayama 2021</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Neuron-specific enolase. Elevated in AD cerebrospinal fluid (Schmidt 2014; meta-analysis in Katayama 2021); reflects neuronal injury with no evidence of a causal role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SNTG1</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.28416392</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3.846748676542297e-157</v>
+      </c>
+      <c r="F8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Velez 2019</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Gamma-1-syntrophin. A variant interacts with APOE e2 to delay onset in PSEN1 E280A carriers in one small cohort (Velez 2019).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>LUC7L3</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.35283738</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.707468400566502e-88</v>
+      </c>
+      <c r="F9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>RBM25</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.50209945</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.513745564190749e-68</v>
+      </c>
+      <c r="F10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ROBO2</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.061422046</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.1220197234444e-17</v>
+      </c>
+      <c r="F11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>SLIT receptor for axon guidance. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KIAA1217</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.06522965999999999</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.328093317299795e-08</v>
+      </c>
+      <c r="F12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Zhang 2016; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Host gene of the primate-specific miR-603. An AD-associated variant lies in the miR-603 precursor (Zhang 2016); no AD studies of KIAA1217 itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ANKRD12</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.4475533</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.897923366348756e-57</v>
+      </c>
+      <c r="F13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Ankyrin repeat transcriptional corepressor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PRRC2C</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.32917583</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>9.785501376641174e-31</v>
+      </c>
+      <c r="F14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Proline-rich coiled-coil protein and stress granule component. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SGCZ</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.119287975</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.811905876464507e-15</v>
+      </c>
+      <c r="F15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Zeta-sarcoglycan of the dystrophin-associated complex. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LINC00342</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-0.11878686</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.757621790043772e-09</v>
+      </c>
+      <c r="F16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Long intergenic noncoding RNA. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ENSG00000274422</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.9888332</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>9.326740078405216e-77</v>
+      </c>
+      <c r="F17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Unannotated transcript without an assigned gene symbol; no AD literature linked to this identifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DYNC2I1</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-0.107587874</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.939190509593427e-07</v>
+      </c>
+      <c r="F18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Intermediate chain of the dynein-2 ciliary transport motor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>MGAT4C</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.09757373</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.470835717150639e-08</v>
+      </c>
+      <c r="F19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Gene 2021; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>N-acetylglucosaminyltransferase for N-glycan branching. One rare deletion in 35 patients with major neurocognitive disorder (Gene 2021); not specific to AD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>PPIG</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.24191454</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>9.143039382956179e-06</v>
+      </c>
+      <c r="F20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Nuclear cyclophilin G associated with splicing factors. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ENSG00000230021</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.5416309</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3.717986044742603e-47</v>
+      </c>
+      <c r="F21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Unannotated transcript without an assigned gene symbol; no AD literature linked to this identifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ZC3H13</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.19416435</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.0005186457807994</v>
+      </c>
+      <c r="F22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Knuckles 2018; Huang 2020</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Component of the m6A (N6-methyladenosine) writer complex (Knuckles 2018). AD studies report altered METTL3 in the same complex (Huang 2020), not ZC3H13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GALNTL6</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-0.09235255000000001</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.0389757839474736</v>
+      </c>
+      <c r="F23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="I23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Polypeptide N-acetylgalactosaminyltransferase for O-linked glycosylation. No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SREK1</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.61310506</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.473914604291229e-32</v>
+      </c>
+      <c r="F24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="I24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Splicing regulatory protein. Its binding partner p18SRP (SREK1IP1), not SREK1, is reduced in AD brain; No AD-specific studies; not a risk locus in large AD GWAS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2613,7 +4549,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>p-value (DE)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2686,7 +4622,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Main astrocytic glutamate transporter (EAAT2/GLT-1); reduced glutamate uptake in AD brain tied to neurodegeneration</t>
+          <t>Principal astrocytic glutamate transporter (EAAT2/GLT-1). Glutamate transport is reduced in AD cortex in proportion to neurodegeneration (Masliah 1996).</t>
         </is>
       </c>
     </row>
@@ -2729,7 +4665,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>lncRNA that regulates glial amyloid-beta clearance through endocytosis genes</t>
+          <t>Nuclear lncRNA. Regulates glial clearance of amyloid-beta through epigenetic control of endocytosis genes (Wang 2019).</t>
         </is>
       </c>
     </row>
@@ -2772,7 +4708,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Present in AD tangles; partner of the Kv4 potassium channel (pathway-level)</t>
+          <t>Dipeptidyl peptidase-like subunit of Kv4 potassium channels. Abnormally expressed and present in neurofibrillary tangles in AD and other neurodegenerative diseases (Chen 2014).</t>
         </is>
       </c>
     </row>
@@ -2815,7 +4751,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Astrocytic Na+/K+ pump that supports glutamate uptake; raised in AD and tauopathy brain, and its blockade reduces neurodegeneration in mice</t>
+          <t>Astrocytic alpha-2 Na+/K+ ATPase that supports glutamate clearance. Increased in AD and tauopathy brain; astrocytic inhibition reduces reactivity and neurodegeneration in a tauopathy mouse model (Mann 2022).</t>
         </is>
       </c>
     </row>
@@ -2858,7 +4794,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Glutamine synthetase (glutamate-glutamine cycle); reduced in AD astrocytes and AD mouse models</t>
+          <t>Glutamine synthetase of the astrocytic glutamate-glutamine cycle. Reduced in hippocampal astrocytes of AD mouse models (Olabarria 2011; Kulijewicz-Nawrot 2013); aberrant neuronal expression in AD brain (Robinson 2000).</t>
         </is>
       </c>
     </row>
@@ -2901,29 +4837,29 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Astrocyte-enriched protein; raised in AD brain (RNA and protein) and found in senile plaques and dystrophic neurites</t>
+          <t>Astrocyte-enriched protein. Increased in AD brain at the RNA and protein level and present in senile plaques and dystrophic neurites (Mitchelmore 2004).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LINC00486</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FGFR3</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5233208</v>
+        <v>-0.638039</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4.624892519005148e-85</v>
+        <v>2.225928833333926e-37</v>
       </c>
       <c r="F8" s="6" t="b">
         <v>0</v>
@@ -2935,12 +4871,16 @@
         <v>0.0384615384615384</v>
       </c>
       <c r="I8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Kim 2024</t>
+        </is>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Fibroblast growth factor receptor 3. Acts as a neuronal receptor for extracellular tau; amyloid-beta promotes FGFR3-mediated tau uptake, and hippocampal knockdown reduces tau aggregation and improves memory in AD model mice (Kim 2024).</t>
         </is>
       </c>
     </row>
@@ -2953,9 +4893,9 @@
           <t>LUC7L3</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -2978,34 +4918,34 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Bishof 2018</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PNISR</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>HPSE2</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.42481253</v>
+        <v>0.21412526</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3.609609424893895e-31</v>
+        <v>7.661865327044269e-11</v>
       </c>
       <c r="F10" s="6" t="b">
         <v>0</v>
@@ -3017,61 +4957,69 @@
         <v>0.0384615384615384</v>
       </c>
       <c r="I10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Garcia 2017</t>
+        </is>
+      </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Heparan sulfate-binding heparanase homolog without enzymatic activity. Increased in AD brain in a stage-dependent manner and present in neuritic plaques (Garcia 2017); expression data only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DLC1</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RBM25</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.0254348</v>
+        <v>0.1532745</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1169001190764857</v>
+        <v>0.4006307502807</v>
       </c>
       <c r="F11" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.1153846153846153</v>
       </c>
       <c r="I11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="8" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MIR9-1HG</t>
+          <t>LINC00486</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -3080,10 +5028,10 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6710748</v>
+        <v>-0.5233208</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>9.987897241090704e-63</v>
+        <v>4.624892519005148e-85</v>
       </c>
       <c r="F12" s="6" t="b">
         <v>0</v>
@@ -3097,20 +5045,24 @@
       <c r="I12" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="8" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Long intergenic noncoding RNA. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SYNE1</t>
+          <t>PNISR</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -3119,10 +5071,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.30007973</v>
+        <v>0.42481253</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3.07256896376835e-17</v>
+        <v>3.609609424893895e-31</v>
       </c>
       <c r="F13" s="6" t="b">
         <v>0</v>
@@ -3134,22 +5086,26 @@
         <v>0.0384615384615384</v>
       </c>
       <c r="I13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Nuclear serine/arginine-rich splicing-associated protein. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COL5A3</t>
+          <t>DLC1</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -3158,10 +5114,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.05132723</v>
+        <v>-0.0254348</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.284219633990057</v>
+        <v>0.1169001190764857</v>
       </c>
       <c r="F14" s="6" t="b">
         <v>1</v>
@@ -3170,25 +5126,29 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I14" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Rho GTPase-activating protein and tumor suppressor. Sub-threshold entry in the GWAS catalog only; No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MGAT4C</t>
+          <t>MIR9-1HG</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -3197,13 +5157,13 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.057244528</v>
+        <v>-0.6710748</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.3236818579655448</v>
+        <v>9.987897241090704e-63</v>
       </c>
       <c r="F15" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
@@ -3212,22 +5172,26 @@
         <v>0.0384615384615384</v>
       </c>
       <c r="I15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Host gene of miR-9-1. AD studies concern miR-9 itself rather than this transcript; No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FGFR3</t>
+          <t>SYNE1</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -3236,10 +5200,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.638039</v>
+        <v>0.30007973</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2.225928833333926e-37</v>
+        <v>3.07256896376835e-17</v>
       </c>
       <c r="F16" s="6" t="b">
         <v>0</v>
@@ -3253,20 +5217,24 @@
       <c r="I16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Nesprin-1 nuclear envelope protein; recessive variants cause cerebellar ataxia. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>HPSE2</t>
+          <t>COL5A3</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -3275,37 +5243,41 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.21412526</v>
+        <v>-0.05132723</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7.661865327044269e-11</v>
+        <v>0.284219633990057</v>
       </c>
       <c r="F17" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="8" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Alpha-3 chain of type V collagen. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TENM2</t>
+          <t>MGAT4C</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -3314,37 +5286,41 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6046328</v>
+        <v>-0.057244528</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>9.57473835096924e-39</v>
+        <v>0.3236818579655448</v>
       </c>
       <c r="F18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0.0384615384615384</v>
       </c>
       <c r="I18" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Gene 2021; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>N-acetylglucosaminyltransferase for N-glycan branching. One rare deletion in 35 patients with major neurocognitive disorder (Gene 2021); not specific to AD.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RBM25</t>
+          <t>TENM2</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -3353,1860 +5329,36 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1532745</v>
+        <v>-0.6046328</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.4006307502807</v>
+        <v>9.57473835096924e-39</v>
       </c>
       <c r="F19" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I19" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+          <t>Med Hypotheses 2015; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Teneurin-2 synaptic adhesion protein. Discussed only in a hypothesis paper on the teneurin family (Med Hypotheses 2015); no AD data for TENM2.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K19"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Bin</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>logFC</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>recurSieve_Unique</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Seed stability</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>recurSieve p-value</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Found in baseline RF</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>WWOX</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.08729035</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>7.701748886382555e-07</v>
-      </c>
-      <c r="F2" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Sze 2004</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>AD risk locus in GWAS; loss increases tau phosphorylation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>NCAM2</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.22656935</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>3.363724983693674e-71</v>
-      </c>
-      <c r="F3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I3" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>Leshchyns'ka 2015; Sytnyk 2017</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>Amyloid-beta removes it from synapses, driving synapse loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>HSP90AA1</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.6729497</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1.611631363929448e-230</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I4" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Dickey 2007; Luo 2007</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Chaperone that stabilizes phospho-tau</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ERBB4</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-0.05952082</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.0037938456457026</v>
-      </c>
-      <c r="F5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Chaudhury 2003; Woo 2011</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>Increased in AD neurons and at plaques</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CNTN5</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.09835521</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>7.047255488836244e-12</v>
-      </c>
-      <c r="F6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Dauar 2023; Whitehouse 2013</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>Risk variant linked to faster progression; brain protein data mixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>DPP10</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-0.04691517</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.3933888731634747</v>
-      </c>
-      <c r="F7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Chen 2014</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>Present in AD tangles; partner of the Kv4 potassium channel (pathway-level)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>HS6ST3</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-0.0344914</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0.9965523604844416</v>
-      </c>
-      <c r="F8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Rauch 2018; Stopschinski 2018</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Heparan sulfate 6-O-sulfation controls tau uptake (pathway-level)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>PDE4B</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-0.029262813</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.0001304924615354</v>
-      </c>
-      <c r="F9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Armstrong 2024</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>Hypomorphic PDE4B prevents memory and brain metabolism deficits in an App knock-in AD mouse; GWAS link is cited secondhand in that paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SNHG14</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.036285296</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2.169560720898356e-38</v>
-      </c>
-      <c r="F10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Cai 2021; Xie 2024; Runte 2001</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>Emerging: expression-only evidence (raised in AD serum in one study; one AD brain cell subcluster in a reanalysis); no genetic or functional AD data. Imprinted lncRNA (long noncoding RNA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>DOCK4</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.07413366</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>4.553924977266265e-05</v>
-      </c>
-      <c r="F11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Bone 2021; Bellenguez 2022</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>Emerging: low-frequency coding variant found only in a joint AD and cardiometabolic trait analysis; not an AD locus in Bellenguez 2022; no functional AD data</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SPOCK1</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.09085624</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1.005503898987354e-07</v>
-      </c>
-      <c r="F12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Ekenel 2025; Bellenguez 2022</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>Emerging: GWAS (genome-wide association study) signal reported by one group and not an AD locus in Bellenguez 2022; only follow-up is a conference abstract in cell lines</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>KCNIP4</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.015608293</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>3.830344240127848e-11</v>
-      </c>
-      <c r="F13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Morohashi 2002; Bellenguez 2022</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>Binds presenilin 2 but does not alter amyloid processing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>RALYL</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.11111467</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>3.437049732044309e-50</v>
-      </c>
-      <c r="F14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>LUC7L3</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.19691005</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6.92225694461615e-44</v>
-      </c>
-      <c r="F15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>COPG2</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-0.051300593</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.0523978305406472</v>
-      </c>
-      <c r="F16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SLC24A2</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0.032657485</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2.3823185962033e-07</v>
-      </c>
-      <c r="F17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I17" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>RBM25</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0.16779387</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>1.969044936991839e-09</v>
-      </c>
-      <c r="F18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>ANKRD12</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0.4575935</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>2.216411671586616e-74</v>
-      </c>
-      <c r="F19" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>FRMD5</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>0.07288448</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2.571019965738418e-10</v>
-      </c>
-      <c r="F20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0.1153846153846153</v>
-      </c>
-      <c r="I20" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>FHIT</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0.12219529</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>4.958546800258247e-12</v>
-      </c>
-      <c r="F21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ROBO2</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-0.14253674</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1.174744392914619e-07</v>
-      </c>
-      <c r="F22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>PLCL1</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.13310342</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0.0050309767432661</v>
-      </c>
-      <c r="F23" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I23" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ELMO1</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0.020089554</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.0004319706725633</v>
-      </c>
-      <c r="F24" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus; individual search found no AD study</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>NPAS3</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>0.20711255</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1.597992110933664e-24</v>
-      </c>
-      <c r="F25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SLC44A1</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>0.15670578</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.0154747679463562</v>
-      </c>
-      <c r="F26" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I26" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>ARAP2</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>0.27938163</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>1.007482785636981e-24</v>
-      </c>
-      <c r="F27" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I27" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>MAN2A1</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>-0.20885615</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>3.201874853020317e-33</v>
-      </c>
-      <c r="F28" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>DPYD</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0.2428678</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>7.083351251966565e-18</v>
-      </c>
-      <c r="F29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>GRID2</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.053968597</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.0033080792048531</v>
-      </c>
-      <c r="F30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I30" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>DIP2B</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0.00021104331</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.0002680158544316</v>
-      </c>
-      <c r="F31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>QKI</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>0.19170265</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.0001341224521875</v>
-      </c>
-      <c r="F32" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I32" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>FRYL</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>0.06093571</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.4398057750248119</v>
-      </c>
-      <c r="F33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>ZEB2</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>-0.12610558</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>1.403294970199935e-13</v>
-      </c>
-      <c r="F34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>TCF12</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>0.040693924</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.5478841195561135</v>
-      </c>
-      <c r="F35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I35" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>ZC3H13</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0.12422563</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0.0306440062356844</v>
-      </c>
-      <c r="F36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>Knuckles 2018; Huang 2020</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>Part of the m6A (N6-methyladenosine) methylation complex; AD evidence is for METTL3, not ZC3H13</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>EDIL3</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>0.31071475</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>1.085984614386102e-32</v>
-      </c>
-      <c r="F37" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus; individual search found no AD study</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>PLXDC2</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0.29034597</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>2.92444674091081e-26</v>
-      </c>
-      <c r="F38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>ZNF91</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-0.108737394</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.568412335075166e-12</v>
-      </c>
-      <c r="F39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>ENSG00000230021</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0.6634869</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>5.454691897364666e-113</v>
-      </c>
-      <c r="F40" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>No GWAS locus (not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>PIP4K2A</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0.2727138</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>7.34739456580919e-07</v>
-      </c>
-      <c r="F41" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I41" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SLAIN1</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0.13132645</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.3643079313496823</v>
-      </c>
-      <c r="F42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I42" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5256,7 +5408,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>p-value (DE)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -5329,7 +5481,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>AD risk locus in GWAS; restrains the microglial inflammatory response and is lost in brain ageing</t>
+          <t>Transcription factor. AD risk locus in Lambert 2013, not genome-wide significant in Kunkle 2019; restrains the microglial inflammatory response and is lost with brain ageing (Deczkowska 2017).</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5524,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Complement C3 is activated in AD brain and drives microglial synapse loss; its loss protects against neurodegeneration in amyloid and tau mouse models</t>
+          <t>Central complement component. Activated in AD brain; mediates microglial synapse elimination, and C3 deficiency protects against synapse loss and neurodegeneration in amyloid and tau mouse models (Hong 2016; Shi 2017; Wu 2019).</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5567,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Polyamine catabolism enzyme; raised in AD hippocampus and entorhinal cortex; drives a tau-induced polyamine stress response in mice</t>
+          <t>Spermidine/spermine N1-acetyltransferase in polyamine catabolism. Increased in AD hippocampus and entorhinal cortex (Mahajan 2020); regulates the tau-induced polyamine stress response, and its knockout alters tau pathology in mice (Sandusky-Beltran 2019).</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5610,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>lncRNA that regulates glial amyloid-beta clearance through endocytosis genes</t>
+          <t>Nuclear lncRNA. Regulates glial clearance of amyloid-beta through epigenetic control of endocytosis genes (Wang 2019).</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5653,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Chaperone that stabilizes phospho-tau</t>
+          <t>Molecular chaperone. Stabilizes phosphorylated tau; HSP90 inhibition promotes tau degradation through CHIP and reduces tau pathology in models (Dickey 2007; Luo 2007).</t>
         </is>
       </c>
     </row>
@@ -5544,60 +5696,60 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>MHC class II invariant chain; binds APP and reduces amyloid-beta production (cell models)</t>
+          <t>MHC class II invariant chain. Binds APP and lowers amyloid-beta production in cell models (Matsuda 2009).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ST6GALNAC3</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Emerging</t>
+          <t>ST6GAL1</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5098326</v>
+        <v>-0.18427704</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.07731847805959e-16</v>
+        <v>8.227264699227735e-07</v>
       </c>
       <c r="F8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I8" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Tang 2023</t>
+          <t>Yang 2026</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Sialyltransferase; expression raised in AD brain; single study</t>
+          <t>Beta-galactoside alpha-2,6-sialyltransferase. Elevated in AD patient cerebrospinal fluid and serum; knockdown lowers BACE1 and amyloid-beta 42 in neuroblastoma cells, and knockout rats show lower brain BACE1 (Yang 2026).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>NAV3</t>
+          <t>ST6GALNAC3</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -5606,53 +5758,53 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.57161295</v>
+        <v>-0.5098326</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>9.230125407467974e-17</v>
+        <v>1.07731847805959e-16</v>
       </c>
       <c r="F9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I9" s="6" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Shioya 2010</t>
+          <t>Tang 2023</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Raised in AD brain through loss of its regulator miR-29a; single study</t>
+          <t>Alpha-2,6-sialyltransferase. Increased expression in AD brain in a single transcriptomic study (Tang 2023).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LINC00486</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>NAV3</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.55113417</v>
+        <v>-0.57161295</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4.026411759241647e-22</v>
+        <v>9.230125407467974e-17</v>
       </c>
       <c r="F10" s="6" t="b">
         <v>0</v>
@@ -5661,37 +5813,41 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.1153846153846153</v>
       </c>
       <c r="I10" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Shioya 2010</t>
+        </is>
+      </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Neuron navigator 3. Increased in AD brain following loss of its regulator miR-29a (Shioya 2010); single study.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ST6GAL1</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>LUC7L3</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.18427704</v>
+        <v>0.27939695</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>8.227264699227735e-07</v>
+        <v>0.0023435213493411</v>
       </c>
       <c r="F11" s="6" t="b">
         <v>0</v>
@@ -5700,43 +5856,47 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0384615384615384</v>
       </c>
       <c r="I11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="8" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LINC02798</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RBM25</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.19315296</v>
+        <v>-0.21095042</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.0268135625233032</v>
+        <v>0.0277337175238447</v>
       </c>
       <c r="F12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -5744,20 +5904,24 @@
       <c r="I12" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="8" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Bishof 2018</t>
+        </is>
+      </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Splicing factor with a basic-acidic dipeptide domain. Interacts with U1-70K and shows increased insolubility in AD brain (Bishof 2018); single study without genetic or in vivo data.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LUC7L3</t>
+          <t>LINC00486</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -5766,10 +5930,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.27939695</v>
+        <v>-0.55113417</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.0023435213493411</v>
+        <v>4.026411759241647e-22</v>
       </c>
       <c r="F13" s="6" t="b">
         <v>0</v>
@@ -5778,10 +5942,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I13" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
@@ -5790,17 +5954,17 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Long intergenic noncoding RNA. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RBM25</t>
+          <t>LINC02798</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5809,16 +5973,16 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.21095042</v>
+        <v>0.19315296</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0277337175238447</v>
+        <v>0.0268135625233032</v>
       </c>
       <c r="F14" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0.0384615384615384</v>
@@ -5833,7 +5997,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>No GWAS locus (not searched individually)</t>
+          <t>Long intergenic noncoding RNA. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -5869,10 +6033,14 @@
       <c r="I15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="8" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Shafiq 2025; Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Chromatin remodeler. Microglial deletion in otherwise healthy mice triggers an interferon response and memory deficits (Shafiq 2025); not studied in AD.</t>
         </is>
       </c>
     </row>
@@ -5908,10 +6076,14 @@
       <c r="I16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Nuclear serine/arginine-rich splicing-associated protein. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -5947,10 +6119,14 @@
       <c r="I17" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Long noncoding RNA studied in cancer. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -5986,10 +6162,14 @@
       <c r="I18" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="8" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Sidekick immunoglobulin-superfamily adhesion molecule. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -6025,10 +6205,14 @@
       <c r="I19" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J19" s="8" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Unannotated transcript without an assigned gene symbol; no AD literature linked to this identifier.</t>
         </is>
       </c>
     </row>
@@ -6064,10 +6248,14 @@
       <c r="I20" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="8" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Synapse differentiation-inducing protein that regulates AMPA receptor clustering. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -6103,10 +6291,14 @@
       <c r="I21" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="8" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Kunkle 2019; Jansen 2019; Bellenguez 2022; Wightman 2021</t>
+        </is>
+      </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Not assessed (new in robustness runs; not searched individually)</t>
+          <t>Pre-mRNA processing factor. No AD-specific studies; not a risk locus in large AD GWAS.</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6376,7 +6568,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Whitehouse IJ, et al. Prion protein is decreased in Alzheimer's brain and inversely correlates with BACE1 activity, amyloid-beta levels and Braak stage. PLoS One. 2013;8:e59554. (CNTN5 unchanged in AD brain)</t>
+          <t>Whitehouse IJ, et al. Prion protein is decreased in Alzheimer's brain and inversely correlates with BACE1 activity, amyloid-beta levels and Braak stage. PLoS One. 2013;8:e59554.</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -6461,7 +6653,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Runte M, et al. The IC-SNURF-SNRPN transcript serves as a host for multiple small nucleolar RNA species and as an antisense RNA for UBE3A. Hum Mol Genet. 2001;10:2687-2700. (imprinting only; not an AD study)</t>
+          <t>Runte M, et al. The IC-SNURF-SNRPN transcript serves as a host for multiple small nucleolar RNA species and as an antisense RNA for UBE3A. Hum Mol Genet. 2001;10:2687-2700.</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -6478,7 +6670,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Qomi Ekenel E, et al. Investigation of Alzheimer's disease-associated effect of SPOCK1 protein on apoptosis in nerve cells. Alzheimers Dement. 2025;21(Suppl 1):e105818. (conference abstract)</t>
+          <t>Qomi Ekenel E, et al. Investigation of Alzheimer's disease-associated effect of SPOCK1 protein on apoptosis in nerve cells. Alzheimers Dement. 2025;21(Suppl 1):e105818.</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -6529,7 +6721,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Knuckles P, et al. Zc3h13/Flacc is required for adenosine methylation by bridging the mRNA-binding factor Rbm15/Spenito to the m6A machinery component Wtap/Fl(2)d. Genes Dev. 2018;32:415-429. (establishes ZC3H13 as an m6A writer complex member)</t>
+          <t>Knuckles P, et al. Zc3h13/Flacc is required for adenosine methylation by bridging the mRNA-binding factor Rbm15/Spenito to the m6A machinery component Wtap/Fl(2)d. Genes Dev. 2018;32:415-429.</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -6711,12 +6903,12 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Stem Cell Reports 2025</t>
+          <t>Zeng 2025</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Thymosin beta 4 as an Alzheimer disease intervention target identified using human brain organoids. Stem Cell Reports. 2025;102601.</t>
+          <t>Zeng PM, Sun XY, Li Y, et al. Thymosin beta 4 as an Alzheimer disease intervention target identified using human brain organoids. Stem Cell Reports. 2025.</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -6835,7 +7027,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Armstrong P, et al. Protective effect of PDE4B subtype-specific inhibition in an App knock-in mouse model for Alzheimer's disease. Neuropsychopharmacology. 2024. (cites the PDE4B GWAS association)</t>
+          <t>Armstrong P, et al. Protective effect of PDE4B subtype-specific inhibition in an App knock-in mouse model for Alzheimer's disease. Neuropsychopharmacology. 2024.</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -6862,179 +7054,478 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s11481-018-9781-x</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Lambert 2013</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Lambert JC, et al. Meta-analysis of 74,046 individuals identifies 11 new susceptibility loci for Alzheimer's disease. Nat Genet. 2013;45:1452-1458.</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/ng.2802</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Lambert 2013</t>
+          <t>Deczkowska 2017</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Lambert JC, et al. Meta-analysis of 74,046 individuals identifies 11 new susceptibility loci for Alzheimer's disease. Nat Genet. 2013;45:1452-1458.</t>
+          <t>Deczkowska A, et al. Mef2C restrains microglial inflammatory response and is lost in brain ageing in an IFN-I-dependent manner. Nat Commun. 2017;8:717.</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/ng.2802</t>
+          <t>https://doi.org/10.1038/s41467-017-00769-0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Deczkowska 2017</t>
+          <t>Hong 2016</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Deczkowska A, et al. Mef2C restrains microglial inflammatory response and is lost in brain ageing in an IFN-I-dependent manner. Nat Commun. 2017;8:717.</t>
+          <t>Hong S, et al. Complement and microglia mediate early synapse loss in Alzheimer mouse models. Science. 2016;352:712-716.</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41467-017-00769-0</t>
+          <t>https://doi.org/10.1126/science.aad8373</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Hong 2016</t>
+          <t>Shi 2017</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Hong S, et al. Complement and microglia mediate early synapse loss in Alzheimer mouse models. Science. 2016;352:712-716.</t>
+          <t>Shi Q, et al. Complement C3 deficiency protects against neurodegeneration in aged plaque-rich APP/PS1 mice. Sci Transl Med. 2017;9:eaaf6295.</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1126/science.aad8373</t>
+          <t>https://doi.org/10.1126/scitranslmed.aaf6295</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Shi 2017</t>
+          <t>Wu 2019</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Shi Q, et al. Complement C3 deficiency protects against neurodegeneration in aged plaque-rich APP/PS1 mice. Sci Transl Med. 2017;9:eaaf6295.</t>
+          <t>Wu T, et al. Complement C3 is activated in human AD brain and is required for neurodegeneration in mouse models of amyloidosis and tauopathy. Cell Rep. 2019;28:2111-2123.</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1126/scitranslmed.aaf6295</t>
+          <t>https://doi.org/10.1016/j.celrep.2019.07.060</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Wu 2019</t>
+          <t>Matsuda 2009</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Wu T, et al. Complement C3 is activated in human AD brain and is required for neurodegeneration in mouse models of amyloidosis and tauopathy. Cell Rep. 2019;28:2111-2123.</t>
+          <t>Matsuda S, Matsuda Y, D'Adamio L. CD74 interacts with APP and suppresses the production of Abeta. Mol Neurodegener. 2009;4:41.</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.celrep.2019.07.060</t>
+          <t>https://doi.org/10.1186/1750-1326-4-41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Matsuda 2009</t>
+          <t>Mahajan 2020</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Matsuda S, Matsuda Y, D'Adamio L. CD74 interacts with APP and suppresses the production of Abeta. Mol Neurodegener. 2009;4:41.</t>
+          <t>Mahajan UV, et al. Dysregulation of multiple metabolic networks related to brain transmethylation and polyamine pathways in Alzheimer disease: a targeted metabolomic and transcriptomic study. PLoS Med. 2020;17:e1003012.</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/1750-1326-4-41</t>
+          <t>https://doi.org/10.1371/journal.pmed.1003012</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Mahajan 2020</t>
+          <t>Sandusky-Beltran 2019</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Mahajan UV, et al. Dysregulation of multiple metabolic networks related to brain transmethylation and polyamine pathways in Alzheimer disease: a targeted metabolomic and transcriptomic study. PLoS Med. 2020;17:e1003012.</t>
+          <t>Sandusky-Beltran LA, et al. Spermidine/spermine-N1-acetyltransferase ablation impacts tauopathy-induced polyamine stress response. Alzheimers Res Ther. 2019;11:58.</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pmed.1003012</t>
+          <t>https://doi.org/10.1186/s13195-019-0507-y</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Sandusky-Beltran 2019</t>
+          <t>Tang 2023</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Sandusky-Beltran LA, et al. Spermidine/spermine-N1-acetyltransferase ablation impacts tauopathy-induced polyamine stress response. Alzheimers Res Ther. 2019;11:58.</t>
+          <t>Tang X, et al. Transcriptomic and glycomic analyses highlight pathway-specific glycosylation alterations unique to Alzheimer's disease. Sci Rep. 2023;13:7816.</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s13195-019-0507-y</t>
+          <t>https://doi.org/10.1038/s41598-023-34787-4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Tang 2023</t>
+          <t>Shioya 2010</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Tang X, et al. Transcriptomic and glycomic analyses highlight pathway-specific glycosylation alterations unique to Alzheimer's disease. Sci Rep. 2023;13:7816.</t>
+          <t>Shioya M, et al. Aberrant microRNA expression in the brains of neurodegenerative diseases: miR-29a decreased in Alzheimer disease brains targets neurone navigator 3. Neuropathol Appl Neurobiol. 2010;36:320-330.</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-023-34787-4</t>
+          <t>https://doi.org/10.1111/j.1365-2990.2010.01076.x</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Shioya 2010</t>
+          <t>Bishof 2018</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Shioya M, et al. Aberrant microRNA expression in the brains of neurodegenerative diseases: miR-29a decreased in Alzheimer disease brains targets neurone navigator 3. Neuropathol Appl Neurobiol. 2010;36:320-330.</t>
+          <t>Bishof I, et al. RNA-binding proteins with basic-acidic dipeptide (BAD) domains self-assemble and aggregate in Alzheimer's disease. J Biol Chem. 2018;293:11047-11066.</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1365-2990.2010.01076.x</t>
+          <t>https://doi.org/10.1074/jbc.RA118.001747</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Wu 2006</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Wu JY, Kar A, Kuo D, Yu B, Havlioglu N. SRp54 (SFRS11), a regulator for tau exon 10 alternative splicing identified by an expression cloning strategy. Mol Cell Biol. 2006;26:6739-6747.</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1128/MCB.00739-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Velez 2019</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Velez JI, et al. Targeting neuroplasticity, cardiovascular, and cognitive-associated genomic variants in familial Alzheimer's disease. Mol Neurobiol. 2019;56:3235-3243.</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6476862</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Farnsworth 2016</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Farnsworth B, Peuckert C, Zimmermann B, Jazin E, Kettunen P, Sors Emilsson L. Gene expression of quaking in sporadic Alzheimer's disease patients is both upregulated and related to expression levels of genes involved in amyloid plaque and neurofibrillary tangle formation. J Alzheimers Dis. 2016;53:209-219.</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3233/JAD-160160</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Garcia 2017</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Garcia B, et al. Upregulated expression of heparanase and heparanase 2 in the brains of Alzheimer's disease. J Alzheimers Dis. 2017;58:185-192.</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3233/JAD-161298</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Oh 2025</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Oh YR, Park SE, Kim HK, Seo H, Shin MK. Microglial PLXDC2 modulates amyloid-beta phagocytosis and inflammatory responses. Biomol Ther (Seoul). 2025;33:952-962.</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4062/biomolther.2025.150</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Yanaizu 2025</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>Yanaizu M, Takata Y, Kato M, Fujiwara H, Kino Y. Transcriptional activation of the TREM2 gene by ZEB2 in a zinc finger-dependent manner. Genes (Basel). 2025;16:1329.</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/genes16111329</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Zhang 2020</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Zhang Y, Wang J, Liu X, Liu H. Exploring the role of RALYL in Alzheimer's disease reserve by network-based approaches. Alzheimers Res Ther. 2020;12:165.</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s13195-020-00733-z</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Kim 2024</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>Kim DK, et al. FGFR3 drives amyloid-beta-induced tau uptake. Exp Mol Med. 2024;56:1631-1642.</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s12276-024-01274-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Yang 2026</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Yang K, Li X, Lai M, Zhao W, Song W, Chen S, Li W. Ablation of ST6Gal-I downregulates BACE1 expression and suppresses production of amyloid-beta 42 plaques in Alzheimer's disease. Engineering. 2026;57:58-71.</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.eng.2025.02.016</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Zhang 2016</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Zhang C, Lu J, Liu B, Cui Q, Wang Y. Primate-specific miR-603 is implicated in the risk and pathogenesis of Alzheimer's disease. Aging. 2016;8.</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.18632/aging.100887</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Gene 2021</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Association of MGAT4C with major neurocognitive disorder in the Mexican population. Gene. 2021;145484.</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.gene.2021.145484</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Sun 2019</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Sun J, Zheng J, Li Y, Yan M, Li P, Ma L. LncRNA EPIC1 downregulation mediates hydrogen peroxide-induced neuronal cell injury. Aging. 2019;11:11463-11473.</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>https://www.aging-us.com/article/102545</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Fagerberg 2020</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Fagerberg CR, et al. Choline transporter-like 1 deficiency causes a new type of childhood-onset neurodegeneration. Brain. 2020;143:94-111.</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/brain/awz376</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Med Hypotheses 2015</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Teneurins and Alzheimer's disease: a suggestive role for a unique family of proteins. Med Hypotheses. 2015;84:402-407.</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.mehy.2015.01.026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Shafiq 2025</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Shafiq S, Ghahramani A, Mansour K, et al. Microglial deficiency in the ATRX chromatin remodeler elicits a viral mimicry immune response that impacts neuronal function and behavior. PLoS Biol. 2025.</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pbio.3002659</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Dube 2019</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Dube U, et al. An atlas of cortical circular RNA expression in Alzheimer disease brains demonstrates clinical and pathological associations. Nat Neurosci. 2019;22:1903-1912.</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41593-019-0501-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>Nguyen 2024</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Nguyen DPQ, Jallow AW, Lin YF, Lin YF. Exploring the potential role of oligodendrocyte-associated PIP4K2A in Alzheimer's disease complicated with type 2 diabetes mellitus via multi-omic analysis. Int J Mol Sci. 2024;25:6640.</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/ijms25126640</t>
         </is>
       </c>
     </row>
@@ -7070,11 +7561,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId37"/>
@@ -7085,6 +7576,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/manuscript/robustness/Supplemental_Table_1.xlsx
+++ b/manuscript/robustness/Supplemental_Table_1.xlsx
@@ -16,11 +16,11 @@
     <sheet name="References" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'All Cell Types'!$A$1:$K$42</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Astrocytes!$A$1:$K$19</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Excitatory!$A$1:$K$24</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Inhibitory!$A$1:$K$24</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Microglia!$A$1:$K$21</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'All Cell Types'!$A$1:$L$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Astrocytes!$A$1:$L$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Excitatory!$A$1:$L$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Inhibitory!$A$1:$L$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Microglia!$A$1:$L$21</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">References!$A$1:$C$54</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="441">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -1354,6 +1354,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.nature.com/articles/s41467-026-68920-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recurSieve adjusted p-value (BH)</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K1048576"/>
+  <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1911,9 +1914,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,12 +1946,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1975,16 +1982,19 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J2" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2012,16 +2022,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I3" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2049,16 +2062,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I4" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2086,16 +2102,19 @@
         <v>0.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2123,16 +2142,19 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I6" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2160,16 +2182,19 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2197,16 +2222,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.0534132360604481</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2234,16 +2262,19 @@
         <v>0.1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I9" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
+        <v>0.0594059405940594</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.0608910891089108</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2271,16 +2302,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J10" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2308,16 +2342,19 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I11" s="6" t="b">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.0534132360604481</v>
+      </c>
+      <c r="J11" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2345,16 +2382,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2382,16 +2422,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="s">
+        <v>0.0693069306930693</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.0693069306930693</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2419,16 +2462,19 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I14" s="6" t="b">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J14" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2456,16 +2502,19 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I15" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2493,16 +2542,19 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.0534132360604481</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2530,16 +2582,19 @@
         <v>0.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I17" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2567,16 +2622,19 @@
         <v>0.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2604,16 +2662,19 @@
         <v>0.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2641,16 +2702,19 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2678,16 +2742,19 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I21" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2715,16 +2782,19 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I22" s="6" t="b">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J22" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2752,16 +2822,19 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.115384615384615</v>
-      </c>
-      <c r="I23" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2789,16 +2862,19 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I24" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2826,16 +2902,19 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I25" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J25" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="L25" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2863,16 +2942,19 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I26" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J26" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="L26" s="8" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2900,16 +2982,19 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I27" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J27" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="L27" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2937,16 +3022,19 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I28" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J28" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2974,16 +3062,19 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I29" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="L29" s="8" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3011,16 +3102,19 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I30" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3048,16 +3142,19 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I31" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J31" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3085,16 +3182,19 @@
         <v>0.9</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I32" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J32" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3122,16 +3222,19 @@
         <v>0.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I33" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J33" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="L33" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3159,16 +3262,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I34" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="8" t="s">
+        <v>0.0594059405940594</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.0608910891089108</v>
+      </c>
+      <c r="J34" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="L34" s="8" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3196,16 +3302,19 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I35" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J35" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="L35" s="8" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3233,16 +3342,19 @@
         <v>0.5</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I36" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J36" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="L36" s="8" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3270,16 +3382,19 @@
         <v>0.8</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I37" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J37" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="L37" s="8" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3307,16 +3422,19 @@
         <v>0.9</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I38" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J38" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="K38" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="L38" s="8" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3344,16 +3462,19 @@
         <v>0.7</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I39" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J39" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K39" s="8" t="s">
+      <c r="L39" s="8" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3381,16 +3502,19 @@
         <v>0.4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I40" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J40" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="K40" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="L40" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3418,16 +3542,19 @@
         <v>0.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I41" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0.0463932107496464</v>
+      </c>
+      <c r="J41" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="L41" s="8" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3455,22 +3582,25 @@
         <v>0.1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I42" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.0434936350777934</v>
+      </c>
+      <c r="J42" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K42" s="8" t="s">
+      <c r="L42" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:L42"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3487,7 +3617,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -3498,9 +3628,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3529,12 +3660,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3562,16 +3696,19 @@
         <v>0.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I2" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3599,16 +3736,19 @@
         <v>0.9</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I3" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3636,16 +3776,19 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.115384615384615</v>
-      </c>
-      <c r="I4" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J4" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3673,16 +3816,19 @@
         <v>0.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.0414041404140414</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3710,16 +3856,19 @@
         <v>0.9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I6" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3747,16 +3896,19 @@
         <v>0.9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3784,16 +3936,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3821,16 +3976,19 @@
         <v>0.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I9" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3858,16 +4016,19 @@
         <v>0.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J10" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3895,16 +4056,19 @@
         <v>0.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="s">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3932,16 +4096,19 @@
         <v>0.9</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I12" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J12" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3969,16 +4136,19 @@
         <v>0.9</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4006,16 +4176,19 @@
         <v>0.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>137</v>
       </c>
     </row>
@@ -4043,16 +4216,19 @@
         <v>0.9</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I15" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4080,16 +4256,19 @@
         <v>0.8</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4117,16 +4296,19 @@
         <v>0.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I17" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4154,16 +4336,19 @@
         <v>0.4</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I18" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J18" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4191,16 +4376,19 @@
         <v>0.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4228,16 +4416,19 @@
         <v>0.2</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4265,16 +4456,19 @@
         <v>0.4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I21" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4302,16 +4496,19 @@
         <v>0.4</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I22" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4339,16 +4536,19 @@
         <v>0.6</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I23" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.0267909143855562</v>
+      </c>
+      <c r="J23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4376,21 +4576,24 @@
         <v>0.2</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I24" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.0227722772277227</v>
+      </c>
+      <c r="J24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:L24"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4407,7 +4610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4418,9 +4621,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4449,12 +4653,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4482,16 +4689,19 @@
         <v>0.8</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.115384615384615</v>
-      </c>
-      <c r="I2" s="6" t="b">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="J2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4519,16 +4729,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I3" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4556,16 +4769,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I4" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4593,16 +4809,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4630,16 +4849,19 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I6" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4667,16 +4889,19 @@
         <v>0.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4704,16 +4929,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I8" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J8" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4741,16 +4969,19 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I9" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4778,16 +5009,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I10" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4815,16 +5049,19 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4852,16 +5089,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4889,16 +5129,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4926,16 +5169,19 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4963,16 +5209,19 @@
         <v>0.9</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I15" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5000,16 +5249,19 @@
         <v>0.9</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5037,16 +5289,19 @@
         <v>0.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I17" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J17" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5074,16 +5329,19 @@
         <v>0.8</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5111,16 +5369,19 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5148,16 +5409,19 @@
         <v>0.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I20" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5185,16 +5449,19 @@
         <v>0.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I21" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J21" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5222,16 +5489,19 @@
         <v>0.6</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I22" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J22" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5259,16 +5529,19 @@
         <v>0.8</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I23" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="J23" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5296,21 +5569,24 @@
         <v>0.4</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I24" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.0325318246110325</v>
+      </c>
+      <c r="J24" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:L24"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5327,7 +5603,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -5338,9 +5614,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5369,12 +5646,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5402,16 +5682,19 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J2" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5439,16 +5722,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I3" s="6" t="b">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="J3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5476,16 +5762,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I4" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J4" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5513,16 +5802,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5550,16 +5842,19 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I6" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5587,16 +5882,19 @@
         <v>0.9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -5624,16 +5922,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5661,16 +5962,19 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I9" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5698,16 +6002,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J10" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5735,16 +6042,19 @@
         <v>0.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.115384615384615</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.0334158415841584</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5772,16 +6082,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I12" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J12" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5809,16 +6122,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I13" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J13" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>139</v>
       </c>
     </row>
@@ -5846,16 +6162,19 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>207</v>
       </c>
     </row>
@@ -5883,16 +6202,19 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I15" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J15" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5920,16 +6242,19 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5957,16 +6282,19 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I17" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="s">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.0396039603960396</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>213</v>
       </c>
     </row>
@@ -5994,16 +6322,19 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.0254596888260254</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>177</v>
       </c>
     </row>
@@ -6031,21 +6362,24 @@
         <v>0.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I19" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0334158415841584</v>
+      </c>
+      <c r="J19" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>137</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:L19"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6062,7 +6396,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6073,9 +6407,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6104,12 +6439,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6137,16 +6475,19 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I2" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>216</v>
       </c>
     </row>
@@ -6174,16 +6515,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I3" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J3" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>219</v>
       </c>
     </row>
@@ -6211,16 +6555,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I4" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.034944670937682</v>
+      </c>
+      <c r="J4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6248,16 +6595,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I5" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>189</v>
       </c>
     </row>
@@ -6285,16 +6635,19 @@
         <v>0.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I6" s="6" t="b">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6322,16 +6675,19 @@
         <v>0.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>225</v>
       </c>
     </row>
@@ -6359,16 +6715,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.034944670937682</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>228</v>
       </c>
     </row>
@@ -6396,16 +6755,19 @@
         <v>0.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I9" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.034944670937682</v>
+      </c>
+      <c r="J9" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>231</v>
       </c>
     </row>
@@ -6433,16 +6795,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.115384615384615</v>
-      </c>
-      <c r="I10" s="6" t="b">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="J10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>234</v>
       </c>
     </row>
@@ -6470,16 +6835,19 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6507,16 +6875,19 @@
         <v>0.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6544,16 +6915,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I13" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J13" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6581,16 +6955,19 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6618,16 +6995,19 @@
         <v>0.5</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I15" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>238</v>
       </c>
     </row>
@@ -6655,16 +7035,19 @@
         <v>0.8</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+        <v>0.0099009900990099</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>139</v>
       </c>
     </row>
@@ -6692,16 +7075,19 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0384615384615384</v>
-      </c>
-      <c r="I17" s="6" t="b">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J17" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6729,16 +7115,19 @@
         <v>0.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I18" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="s">
+        <v>0.0198019801980198</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.033003300330033</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>242</v>
       </c>
     </row>
@@ -6766,16 +7155,19 @@
         <v>0.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="s">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0495049504950495</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6803,16 +7195,19 @@
         <v>0.9</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I20" s="6" t="b">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.034944670937682</v>
+      </c>
+      <c r="J20" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>245</v>
       </c>
     </row>
@@ -6840,21 +7235,24 @@
         <v>0.4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="I21" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="s">
+        <v>0.0297029702970297</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.034944670937682</v>
+      </c>
+      <c r="J21" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>247</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:L21"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
